--- a/output/pdf_financials_xlsx/LEXT.xlsx
+++ b/output/pdf_financials_xlsx/LEXT.xlsx
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.151462</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.127772</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.034582</v>
       </c>
     </row>
     <row r="93">
@@ -3123,7 +3123,11 @@
           <t>Share-based payment reserves 10,12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3278,7 +3282,11 @@
           <t>Share-based payment reserves 10,11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.151462</v>
       </c>

--- a/output/pdf_financials_xlsx/LEXT.xlsx
+++ b/output/pdf_financials_xlsx/LEXT.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.510995</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.390405</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002322</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.510995</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.390405</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002322</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.75132</v>
+        <v>0.240325</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.444405</v>
+        <v>0.054</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.163446</v>
+        <v>0.161124</v>
       </c>
     </row>
     <row r="49">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/LEXT.xlsx
+++ b/output/pdf_financials_xlsx/LEXT.xlsx
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1.108744</v>
+        <v>-0.966068</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.867713</v>
+        <v>-0.734282</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.616816</v>
+        <v>-1.540476</v>
       </c>
     </row>
     <row r="21">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.142676</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.133431</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.07634000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3722,7 +3722,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.908242</v>
       </c>
@@ -4621,7 +4625,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>-0.966068</v>
       </c>
@@ -4648,7 +4656,11 @@
           <t>Loss from discontinued operations 15</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5413,7 +5425,11 @@
           <t>Loss from discontinued operations 14</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>-0.142676</v>
       </c>
